--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -8,30 +8,31 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F01A98F5-C369-4BC9-8F06-3CEFE60A8657}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D139B8-C64A-468C-B595-A0AD42437487}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
-    <sheet name="CreationWithOnlyPaymentDetail" sheetId="20" r:id="rId2"/>
-    <sheet name="PrimaryRepresentativeDetails" sheetId="14" r:id="rId3"/>
-    <sheet name="OrgAddressOtherThanUSA" sheetId="13" r:id="rId4"/>
-    <sheet name="CreationQ1NO" sheetId="19" r:id="rId5"/>
-    <sheet name="UniqueOrgInfoQuestionsNoExplain" sheetId="15" r:id="rId6"/>
-    <sheet name="WithQues1YesDetailExplain" sheetId="16" r:id="rId7"/>
-    <sheet name="WithQues1YesNICRAYes" sheetId="17" r:id="rId8"/>
-    <sheet name="WithQues1YesOrgIncorYes" sheetId="18" r:id="rId9"/>
-    <sheet name="Question1" sheetId="2" r:id="rId10"/>
-    <sheet name="Question2" sheetId="4" r:id="rId11"/>
-    <sheet name="Question1No" sheetId="3" r:id="rId12"/>
-    <sheet name="Question2No" sheetId="5" r:id="rId13"/>
-    <sheet name="UniqueOrgInfoQuestions" sheetId="6" r:id="rId14"/>
-    <sheet name="OrgAddress" sheetId="7" r:id="rId15"/>
-    <sheet name="OrgProfile" sheetId="8" r:id="rId16"/>
-    <sheet name="OrgProfileCompleteDetail" sheetId="9" r:id="rId17"/>
-    <sheet name="WithQues1YesAndRelatedDetailsNo" sheetId="11" r:id="rId18"/>
-    <sheet name="WithQues1YesAndRelatedDetailYes" sheetId="12" r:id="rId19"/>
+    <sheet name="OrgRegCreationCompleteDetail" sheetId="21" r:id="rId2"/>
+    <sheet name="CreationWithOnlyPaymentDetail" sheetId="20" r:id="rId3"/>
+    <sheet name="PrimaryRepresentativeDetails" sheetId="14" r:id="rId4"/>
+    <sheet name="OrgAddressOtherThanUSA" sheetId="13" r:id="rId5"/>
+    <sheet name="CreationQ1NO" sheetId="19" r:id="rId6"/>
+    <sheet name="UniqueOrgInfoQuestionsNoExplain" sheetId="15" r:id="rId7"/>
+    <sheet name="WithQues1YesDetailExplain" sheetId="16" r:id="rId8"/>
+    <sheet name="WithQues1YesNICRAYes" sheetId="17" r:id="rId9"/>
+    <sheet name="WithQues1YesOrgIncorYes" sheetId="18" r:id="rId10"/>
+    <sheet name="Question1" sheetId="2" r:id="rId11"/>
+    <sheet name="Question2" sheetId="4" r:id="rId12"/>
+    <sheet name="Question1No" sheetId="3" r:id="rId13"/>
+    <sheet name="Question2No" sheetId="5" r:id="rId14"/>
+    <sheet name="UniqueOrgInfoQuestions" sheetId="6" r:id="rId15"/>
+    <sheet name="OrgAddress" sheetId="7" r:id="rId16"/>
+    <sheet name="OrgProfile" sheetId="8" r:id="rId17"/>
+    <sheet name="OrgProfileCompleteDetail" sheetId="9" r:id="rId18"/>
+    <sheet name="WithQues1YesAndRelatedDetailsNo" sheetId="11" r:id="rId19"/>
+    <sheet name="WithQues1YesAndRelatedDetailYes" sheetId="12" r:id="rId20"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="90">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -937,6 +938,107 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F6A843-34CB-40B2-914A-08E2C54EB350}">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="28.46484375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A00A2F9B-1F15-474D-9DD4-993171530508}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -972,7 +1074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05EFA198-FBA1-4B9A-B3E9-28166FF18612}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1008,7 +1110,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF1A298F-7844-48D1-98DD-53D7D86DE791}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1043,7 +1145,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69C6C8DD-009D-425E-9B69-09D5E0ACEE9D}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1078,7 +1180,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2F0CAC-30A4-45BD-AE27-07806349BD24}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1125,7 +1227,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5343F989-BED4-4C3F-AE8F-330830F9208D}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1220,7 +1322,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B216D1F-84FF-4062-A939-3C635B054F5E}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1279,7 +1381,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C7FB28-3C46-41CD-B1C8-5ACD5AA83D43}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1360,7 +1462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B080C06C-48BE-4956-AB6C-FA9A46DD80B4}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1430,7 +1532,168 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656D3EEC-31AD-4355-BD03-CC983BBF34F9}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="8.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="22">
+        <v>20171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{FA019F3C-CAF3-40BA-A6D4-430C2E40DA3F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44E55028-70E0-4DC2-93F0-398F08D85BA5}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1511,7 +1774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9428DC2-E37D-4A86-AEA0-C4AB0CF98F92}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1630,7 +1893,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4BF3096-62C1-489E-B677-AEC71181CA96}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1778,7 +2041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCE78A5-F6A7-4E3D-A256-8FF61363066F}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1873,7 +2136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C74A7102-EF70-435E-8D51-B513DF0574A2}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1968,7 +2231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B84EBB0-BE12-4675-B5CC-0B8071F9EF1D}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2022,7 +2285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6905C96-681E-4E14-B81E-3B11E237FCA3}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2120,7 +2383,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1AA2095-5BE4-441A-914C-113834C7CAC4}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -2205,105 +2468,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F6A843-34CB-40B2-914A-08E2C54EB350}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="2" max="2" width="28.46484375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D139B8-C64A-468C-B595-A0AD42437487}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6262F274-A2EB-42EB-A56C-6FFED084C487}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
-    <sheet name="OrgRegCreationCompleteDetail" sheetId="21" r:id="rId2"/>
-    <sheet name="CreationWithOnlyPaymentDetail" sheetId="20" r:id="rId3"/>
-    <sheet name="PrimaryRepresentativeDetails" sheetId="14" r:id="rId4"/>
+    <sheet name="AuthorizedRepresentativeDetails" sheetId="14" r:id="rId2"/>
+    <sheet name="OrgRegCreationCompleteDetail" sheetId="21" r:id="rId3"/>
+    <sheet name="CreationWithOnlyPaymentDetail" sheetId="20" r:id="rId4"/>
     <sheet name="OrgAddressOtherThanUSA" sheetId="13" r:id="rId5"/>
     <sheet name="CreationQ1NO" sheetId="19" r:id="rId6"/>
     <sheet name="UniqueOrgInfoQuestionsNoExplain" sheetId="15" r:id="rId7"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="90">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -181,9 +181,6 @@
     <t>User</t>
   </si>
   <si>
-    <t>Automation Primary Representative</t>
-  </si>
-  <si>
     <t>fieldOrgNotLegalExplanation_NED__c</t>
   </si>
   <si>
@@ -307,13 +304,16 @@
     <t>fieldPrimaryRepZipCode__c</t>
   </si>
   <si>
-    <t>fieldPrimaryRepZipCode4__c</t>
-  </si>
-  <si>
     <t>fieldPrimaryRepCountry__c</t>
   </si>
   <si>
     <t>fieldPrimaryRepPhone__c</t>
+  </si>
+  <si>
+    <t>Automation Representative</t>
+  </si>
+  <si>
+    <t>fieldPrimaryRepEmail__c</t>
   </si>
 </sst>
 </file>
@@ -778,7 +778,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="32.46484375" customWidth="1"/>
@@ -804,7 +804,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -812,10 +812,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>60</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -834,21 +834,21 @@
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C5" s="23" t="s">
-        <v>63</v>
-      </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="22" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>65</v>
+        <v>16</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -856,10 +856,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>23</v>
+        <v>65</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -867,10 +867,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>67</v>
+        <v>17</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -878,10 +878,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -889,10 +889,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -900,10 +900,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>71</v>
+        <v>19</v>
+      </c>
+      <c r="C11" s="22">
+        <v>20171</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -911,20 +911,9 @@
         <v>3</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="22">
-        <v>20171</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="22" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1005,7 +994,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -1016,7 +1005,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
         <v>6</v>
@@ -1027,7 +1016,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1310,7 +1299,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1350,7 +1339,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1409,7 +1398,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1533,79 +1522,79 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656D3EEC-31AD-4355-BD03-CC983BBF34F9}">
-  <dimension ref="A1:C13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4BF3096-62C1-489E-B677-AEC71181CA96}">
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="8.06640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.9296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="27" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>59</v>
+      <c r="A2" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="22" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>61</v>
+        <v>42</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="22" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="22" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>63</v>
+        <v>81</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="22" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>65</v>
+        <v>83</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1613,10 +1602,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1624,10 +1613,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>67</v>
+        <v>85</v>
+      </c>
+      <c r="C8" s="22">
+        <v>20301</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1635,61 +1624,40 @@
         <v>3</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>22</v>
+        <v>86</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>68</v>
+      <c r="B10" s="10" t="s">
+        <v>87</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="22">
-        <v>20171</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>24</v>
+      <c r="B11" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{FA019F3C-CAF3-40BA-A6D4-430C2E40DA3F}"/>
+    <hyperlink ref="C11" r:id="rId1" xr:uid="{31CE7BEB-B82F-4E74-A3FD-BDA910AF888E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1775,6 +1743,167 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656D3EEC-31AD-4355-BD03-CC983BBF34F9}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="8.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.06640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="22">
+        <v>20171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{FA019F3C-CAF3-40BA-A6D4-430C2E40DA3F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9428DC2-E37D-4A86-AEA0-C4AB0CF98F92}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1801,7 +1930,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" s="20" t="s">
         <v>6</v>
@@ -1814,10 +1943,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
@@ -1827,10 +1956,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="19"/>
@@ -1840,10 +1969,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19"/>
@@ -1853,7 +1982,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C6" s="22">
         <v>20301</v>
@@ -1866,7 +1995,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="22">
         <v>1234</v>
@@ -1879,161 +2008,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>24</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="19"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4BF3096-62C1-489E-B677-AEC71181CA96}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C8" s="22">
-        <v>20301</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="22">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>24</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2124,7 +2105,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -2165,7 +2146,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2209,7 +2190,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2274,10 +2255,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
         <v>46</v>
-      </c>
-      <c r="C4" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2350,7 +2331,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -2361,10 +2342,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2375,7 +2356,7 @@
         <v>35</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2448,7 +2429,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -2459,10 +2440,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6262F274-A2EB-42EB-A56C-6FFED084C487}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="10395" firstSheet="18" activeTab="20"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -33,10 +27,11 @@
     <sheet name="OrgProfileCompleteDetail" sheetId="9" r:id="rId18"/>
     <sheet name="WithQues1YesAndRelatedDetailsNo" sheetId="11" r:id="rId19"/>
     <sheet name="WithQues1YesAndRelatedDetailYes" sheetId="12" r:id="rId20"/>
+    <sheet name="PrimaryRepresentativeDetails" sheetId="22" r:id="rId21"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <calcPr calcId="124519"/>
+  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -44,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="90">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -319,8 +314,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,6 +397,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -450,7 +451,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -497,6 +498,7 @@
     <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -558,7 +560,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -593,7 +595,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -770,19 +772,19 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="32.46484375" customWidth="1"/>
-    <col min="3" max="3" width="51.33203125" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -919,7 +921,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{DDC17E93-7198-4524-8957-1A865D41B800}"/>
+    <hyperlink ref="C5" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -927,11 +929,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14F6A843-34CB-40B2-914A-08E2C54EB350}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.46484375" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1028,12 +1030,12 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A00A2F9B-1F15-474D-9DD4-993171530508}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.46484375" customWidth="1"/>
-    <col min="3" max="3" width="17.796875" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1064,11 +1066,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05EFA198-FBA1-4B9A-B3E9-28166FF18612}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1100,11 +1102,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF1A298F-7844-48D1-98DD-53D7D86DE791}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="18.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1135,11 +1137,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69C6C8DD-009D-425E-9B69-09D5E0ACEE9D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.46484375" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1170,12 +1172,12 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E2F0CAC-30A4-45BD-AE27-07806349BD24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.53125" customWidth="1"/>
-    <col min="3" max="3" width="19.19921875" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1217,12 +1219,12 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5343F989-BED4-4C3F-AE8F-330830F9208D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.53125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.796875" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1304,7 +1306,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" xr:uid="{E3BFCD58-FA2A-4966-BD19-64EB9BEA4275}"/>
+    <hyperlink ref="C7" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -1312,12 +1314,12 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B216D1F-84FF-4062-A939-3C635B054F5E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1371,12 +1373,12 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C7FB28-3C46-41CD-B1C8-5ACD5AA83D43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1452,12 +1454,12 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B080C06C-48BE-4956-AB6C-FA9A46DD80B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1522,13 +1524,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4BF3096-62C1-489E-B677-AEC71181CA96}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1654,7 +1656,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C11" r:id="rId1" xr:uid="{31CE7BEB-B82F-4E74-A3FD-BDA910AF888E}"/>
+    <hyperlink ref="C11" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -1662,12 +1664,12 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44E55028-70E0-4DC2-93F0-398F08D85BA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1742,14 +1744,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656D3EEC-31AD-4355-BD03-CC983BBF34F9}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.06640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1767,6 +1768,154 @@
       <c r="A2" s="24" t="s">
         <v>3</v>
       </c>
+      <c r="B2" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="22">
+        <v>20301</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="22"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="22"/>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" s="22"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="22"/>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="22"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="22"/>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="22"/>
+      <c r="B13" s="28"/>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="22"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="22"/>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="22"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="22"/>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="22"/>
+      <c r="B16" s="28"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="24" t="s">
+        <v>3</v>
+      </c>
       <c r="B2" s="24" t="s">
         <v>8</v>
       </c>
@@ -1897,19 +2046,19 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{FA019F3C-CAF3-40BA-A6D4-430C2E40DA3F}"/>
+    <hyperlink ref="C5" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9428DC2-E37D-4A86-AEA0-C4AB0CF98F92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="36.06640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2023,12 +2172,12 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BCE78A5-F6A7-4E3D-A256-8FF61363066F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.53125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.06640625" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2110,7 +2259,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" xr:uid="{1776500D-09B5-4C4F-834B-663A02756082}"/>
+    <hyperlink ref="C7" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -2118,13 +2267,13 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C74A7102-EF70-435E-8D51-B513DF0574A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" customWidth="1"/>
-    <col min="2" max="2" width="20.73046875" customWidth="1"/>
-    <col min="3" max="3" width="43.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="43.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2206,16 +2355,16 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C6" r:id="rId1" display="automation.jim@yopmail.com" xr:uid="{DFE520AC-F5D2-4C54-902E-5C4B88B397B6}"/>
+    <hyperlink ref="C6" r:id="rId1" display="automation.jim@yopmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B84EBB0-BE12-4675-B5CC-0B8071F9EF1D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -2267,9 +2416,9 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6905C96-681E-4E14-B81E-3B11E237FCA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="12" t="s">
@@ -2365,9 +2514,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1AA2095-5BE4-441A-914C-113834C7CAC4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="12" t="s">

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39297CE6-083E-4433-B4B8-836DD2BCB568}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="19395" windowHeight="10395" firstSheet="18" activeTab="20"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -30,8 +36,8 @@
     <sheet name="PrimaryRepresentativeDetails" sheetId="22" r:id="rId21"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -39,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="91">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -309,12 +315,15 @@
   </si>
   <si>
     <t>fieldPrimaryRepEmail__c</t>
+  </si>
+  <si>
+    <t>AutomationInternal@yopmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="14">
     <font>
       <sz val="11"/>
@@ -772,19 +781,19 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" customWidth="1"/>
+    <col min="2" max="2" width="32.3984375" customWidth="1"/>
+    <col min="3" max="3" width="51.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -921,7 +930,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1"/>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -929,11 +938,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1030,12 +1039,12 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="20.3984375" customWidth="1"/>
+    <col min="3" max="3" width="17.86328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1066,11 +1075,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1102,11 +1111,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1137,11 +1146,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1172,12 +1181,12 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.59765625" customWidth="1"/>
+    <col min="3" max="3" width="19.1328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1219,12 +1228,12 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.86328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1306,7 +1315,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1"/>
+    <hyperlink ref="C7" r:id="rId1" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -1314,12 +1323,12 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1373,12 +1382,12 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1454,12 +1463,12 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1524,13 +1533,13 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1651,12 +1660,12 @@
         <v>89</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C11" r:id="rId1"/>
+    <hyperlink ref="C11" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -1664,12 +1673,12 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1745,11 +1754,11 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.59765625" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1892,13 +1901,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2046,19 +2055,19 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1"/>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2172,11 +2181,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2259,7 +2268,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1"/>
+    <hyperlink ref="C7" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -2267,13 +2276,13 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.265625" customWidth="1"/>
+    <col min="2" max="2" width="20.73046875" customWidth="1"/>
+    <col min="3" max="3" width="43.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2355,16 +2364,16 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C6" r:id="rId1" display="automation.jim@yopmail.com"/>
+    <hyperlink ref="C6" r:id="rId1" display="automation.jim@yopmail.com" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -2416,9 +2425,9 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="12" t="s">
@@ -2514,9 +2523,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="12" t="s">

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39297CE6-083E-4433-B4B8-836DD2BCB568}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F73E74-9E1A-4A0D-BBEB-5704D38EF630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="150" yWindow="60" windowWidth="20370" windowHeight="10920" firstSheet="19" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -221,9 +221,6 @@
     <t>AutomationOrganization@yopmail.com</t>
   </si>
   <si>
-    <t>AUTOMATION RUNTIME Organization</t>
-  </si>
-  <si>
     <t>fieldOrganizationTypeSInglePicklist__c</t>
   </si>
   <si>
@@ -318,6 +315,12 @@
   </si>
   <si>
     <t>AutomationInternal@yopmail.com</t>
+  </si>
+  <si>
+    <t>Automation Runtime Organization</t>
+  </si>
+  <si>
+    <t>Automation Runtime</t>
   </si>
 </sst>
 </file>
@@ -790,10 +793,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="32.3984375" customWidth="1"/>
-    <col min="3" max="3" width="51.265625" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -815,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -823,10 +826,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>59</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -845,10 +848,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>61</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -867,10 +870,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>65</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -889,10 +892,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="22" t="s">
         <v>67</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -900,10 +903,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="22" t="s">
         <v>69</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -922,7 +925,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" s="22" t="s">
         <v>24</v>
@@ -940,9 +943,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.3984375" customWidth="1"/>
+    <col min="2" max="2" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1041,10 +1044,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.3984375" customWidth="1"/>
-    <col min="3" max="3" width="17.86328125" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1077,9 +1080,9 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1113,9 +1116,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1148,9 +1151,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.3984375" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1183,10 +1186,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="13.59765625" customWidth="1"/>
-    <col min="3" max="3" width="19.1328125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1230,10 +1233,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.86328125" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1325,10 +1328,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="25.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1384,10 +1387,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.59765625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1465,10 +1468,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="22.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1535,11 +1538,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1572,7 +1575,7 @@
         <v>42</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1591,10 +1594,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1602,10 +1605,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1613,10 +1616,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1624,7 +1627,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" s="22">
         <v>20301</v>
@@ -1635,10 +1638,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1646,7 +1649,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C10" s="22" t="s">
         <v>24</v>
@@ -1657,10 +1660,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1675,10 +1678,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="22.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1755,10 +1758,10 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="39.59765625" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1781,7 +1784,7 @@
         <v>42</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1800,10 +1803,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1811,10 +1814,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1822,10 +1825,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1833,7 +1836,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C7" s="22">
         <v>20301</v>
@@ -1844,10 +1847,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1855,44 +1858,11 @@
         <v>3</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C9" s="22" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="22"/>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="22"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="22"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="22"/>
-      <c r="B13" s="28"/>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="22"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="22"/>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="22"/>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1903,11 +1873,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1929,7 +1899,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1937,10 +1907,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>59</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1959,10 +1929,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>61</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1970,10 +1940,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="24" t="s">
         <v>63</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1992,10 +1962,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="21" t="s">
         <v>65</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2014,10 +1984,10 @@
         <v>3</v>
       </c>
       <c r="B10" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="22" t="s">
         <v>67</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2025,10 +1995,10 @@
         <v>3</v>
       </c>
       <c r="B11" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="22" t="s">
         <v>69</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2047,7 +2017,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C13" s="22" t="s">
         <v>24</v>
@@ -2064,10 +2034,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2088,7 +2058,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" s="20" t="s">
         <v>6</v>
@@ -2101,10 +2071,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
@@ -2114,10 +2084,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="19"/>
@@ -2127,10 +2097,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="19"/>
@@ -2140,7 +2110,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C6" s="22">
         <v>20301</v>
@@ -2153,7 +2123,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" s="22">
         <v>1234</v>
@@ -2166,7 +2136,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C8" s="22" t="s">
         <v>24</v>
@@ -2183,9 +2153,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2278,11 +2248,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.265625" customWidth="1"/>
-    <col min="2" max="2" width="20.73046875" customWidth="1"/>
-    <col min="3" max="3" width="43.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="43.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2373,7 +2343,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -2427,7 +2397,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="12" t="s">
@@ -2525,7 +2495,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="12" t="s">

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,39 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F73E74-9E1A-4A0D-BBEB-5704D38EF630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675BFBA7-8D01-4E12-AE84-40D22BAE8D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="150" yWindow="60" windowWidth="20370" windowHeight="10920" firstSheet="19" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15" yWindow="15" windowWidth="20370" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
-    <sheet name="AuthorizedRepresentativeDetails" sheetId="14" r:id="rId2"/>
-    <sheet name="OrgRegCreationCompleteDetail" sheetId="21" r:id="rId3"/>
-    <sheet name="CreationWithOnlyPaymentDetail" sheetId="20" r:id="rId4"/>
-    <sheet name="OrgAddressOtherThanUSA" sheetId="13" r:id="rId5"/>
-    <sheet name="CreationQ1NO" sheetId="19" r:id="rId6"/>
-    <sheet name="UniqueOrgInfoQuestionsNoExplain" sheetId="15" r:id="rId7"/>
-    <sheet name="WithQues1YesDetailExplain" sheetId="16" r:id="rId8"/>
-    <sheet name="WithQues1YesNICRAYes" sheetId="17" r:id="rId9"/>
-    <sheet name="WithQues1YesOrgIncorYes" sheetId="18" r:id="rId10"/>
-    <sheet name="Question1" sheetId="2" r:id="rId11"/>
-    <sheet name="Question2" sheetId="4" r:id="rId12"/>
-    <sheet name="Question1No" sheetId="3" r:id="rId13"/>
-    <sheet name="Question2No" sheetId="5" r:id="rId14"/>
-    <sheet name="UniqueOrgInfoQuestions" sheetId="6" r:id="rId15"/>
-    <sheet name="OrgAddress" sheetId="7" r:id="rId16"/>
-    <sheet name="OrgProfile" sheetId="8" r:id="rId17"/>
-    <sheet name="OrgProfileCompleteDetail" sheetId="9" r:id="rId18"/>
-    <sheet name="WithQues1YesAndRelatedDetailsNo" sheetId="11" r:id="rId19"/>
-    <sheet name="WithQues1YesAndRelatedDetailYes" sheetId="12" r:id="rId20"/>
-    <sheet name="PrimaryRepresentativeDetails" sheetId="22" r:id="rId21"/>
+    <sheet name="parentOrg" sheetId="23" r:id="rId2"/>
+    <sheet name="AuthorizedRepresentativeDetails" sheetId="14" r:id="rId3"/>
+    <sheet name="OrgRegCreationCompleteDetail" sheetId="21" r:id="rId4"/>
+    <sheet name="CreationWithOnlyPaymentDetail" sheetId="20" r:id="rId5"/>
+    <sheet name="OrgAddressOtherThanUSA" sheetId="13" r:id="rId6"/>
+    <sheet name="CreationQ1NO" sheetId="19" r:id="rId7"/>
+    <sheet name="UniqueOrgInfoQuestionsNoExplain" sheetId="15" r:id="rId8"/>
+    <sheet name="WithQues1YesDetailExplain" sheetId="16" r:id="rId9"/>
+    <sheet name="WithQues1YesNICRAYes" sheetId="17" r:id="rId10"/>
+    <sheet name="WithQues1YesOrgIncorYes" sheetId="18" r:id="rId11"/>
+    <sheet name="Question1" sheetId="2" r:id="rId12"/>
+    <sheet name="Question2" sheetId="4" r:id="rId13"/>
+    <sheet name="Question1No" sheetId="3" r:id="rId14"/>
+    <sheet name="Question2No" sheetId="5" r:id="rId15"/>
+    <sheet name="UniqueOrgInfoQuestions" sheetId="6" r:id="rId16"/>
+    <sheet name="OrgAddress" sheetId="7" r:id="rId17"/>
+    <sheet name="OrgProfile" sheetId="8" r:id="rId18"/>
+    <sheet name="OrgProfileCompleteDetail" sheetId="9" r:id="rId19"/>
+    <sheet name="WithQues1YesAndRelatedDetailsNo" sheetId="11" r:id="rId20"/>
+    <sheet name="WithQues1YesAndRelatedDetailYes" sheetId="12" r:id="rId21"/>
+    <sheet name="PrimaryRepresentativeDetails" sheetId="22" r:id="rId22"/>
   </sheets>
   <calcPr calcId="124519"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="93">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -321,13 +322,16 @@
   </si>
   <si>
     <t>Automation Runtime</t>
+  </si>
+  <si>
+    <t>fieldEffectiveDate__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,6 +419,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -463,7 +473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -511,6 +521,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -941,6 +952,93 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1041,7 +1139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1077,7 +1175,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1113,7 +1211,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1148,7 +1246,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1183,7 +1281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1230,7 +1328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1325,7 +1423,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1384,7 +1482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1465,7 +1563,54 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828E63F-C4C2-4AE0-A0E9-A1CABDF6D980}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1535,7 +1680,202 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4">
+        <v>987654321</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="22">
+        <v>20301</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1675,202 +2015,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4">
-        <v>987654321</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="39.5703125" customWidth="1"/>
-    <col min="3" max="3" width="45" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="22">
-        <v>20301</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2031,7 +2176,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2150,7 +2295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2245,7 +2390,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2340,7 +2485,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2394,7 +2539,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2490,91 +2635,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675BFBA7-8D01-4E12-AE84-40D22BAE8D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E125DD-DADC-4C43-9E95-0C58396DCE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="20370" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="94">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>fieldEffectiveDate__c</t>
+  </si>
+  <si>
+    <t>For-profit organizations</t>
   </si>
 </sst>
 </file>
@@ -473,7 +476,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -489,14 +492,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -508,12 +508,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -811,134 +809,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="24" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="19" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>58</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="18" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="21" t="s">
+      <c r="A10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="19">
         <v>20171</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="21" t="s">
+      <c r="A12" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="19" t="s">
         <v>24</v>
       </c>
     </row>
@@ -957,29 +955,29 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -990,7 +988,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -1001,7 +999,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -1012,7 +1010,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -1023,7 +1021,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -1047,29 +1045,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -1080,7 +1078,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -1091,7 +1089,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -1102,7 +1100,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -1113,7 +1111,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -1124,7 +1122,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -1492,13 +1490,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1531,7 +1529,7 @@
       <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1539,10 +1537,10 @@
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="9" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1550,10 +1548,10 @@
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="9" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1573,21 +1571,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
@@ -1595,10 +1593,10 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="29" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>92</v>
       </c>
       <c r="C3">
@@ -1771,101 +1769,101 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="28" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="19" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="28" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="19" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="28" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="28" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="19" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="28" t="s">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="19" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="28" t="s">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="19">
         <v>20301</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="28" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="28" t="s">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="19" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1886,117 +1884,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="19" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="19" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="19" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="19" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="19" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="19">
         <v>20301</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="10" t="s">
@@ -2026,145 +2024,145 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="24" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="19" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="19" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="19" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="18" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="21" t="s">
+      <c r="A10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="21" t="s">
+      <c r="A12" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="19">
         <v>20171</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="21" t="s">
+      <c r="A13" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="19" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2186,108 +2184,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="19">
         <v>20301</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="19">
         <v>1234</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2545,29 +2543,29 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -2578,7 +2576,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
@@ -2589,7 +2587,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -2600,7 +2598,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -2611,7 +2609,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -2622,13 +2620,13 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="13" t="s">
         <v>49</v>
       </c>
     </row>

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E125DD-DADC-4C43-9E95-0C58396DCE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CFA522D-7319-4995-91B9-6A4728945412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>For-profit organizations</t>
+  </si>
+  <si>
+    <t>Prince George</t>
   </si>
 </sst>
 </file>
@@ -882,7 +885,7 @@
         <v>64</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:3">

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CFA522D-7319-4995-91B9-6A4728945412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92C0C68-9119-4142-9796-D6EAA04F77FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92C0C68-9119-4142-9796-D6EAA04F77FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4218C10B-D259-4A80-B736-055BF5EF2F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1764,7 +1764,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="39.5703125" customWidth="1"/>
@@ -1783,14 +1783,14 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>42</v>
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>40</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1798,10 +1798,10 @@
         <v>3</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>44</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1809,10 +1809,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1820,10 +1820,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1831,10 +1831,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1842,10 +1842,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="19">
-        <v>20301</v>
+        <v>83</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1853,10 +1853,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>69</v>
+        <v>84</v>
+      </c>
+      <c r="C8" s="19">
+        <v>20301</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -1864,9 +1864,20 @@
         <v>3</v>
       </c>
       <c r="B9" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C10" s="19" t="s">
         <v>24</v>
       </c>
     </row>

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675BFBA7-8D01-4E12-AE84-40D22BAE8D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4218C10B-D259-4A80-B736-055BF5EF2F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15" yWindow="15" windowWidth="20370" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="95">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -325,6 +325,12 @@
   </si>
   <si>
     <t>fieldEffectiveDate__c</t>
+  </si>
+  <si>
+    <t>For-profit organizations</t>
+  </si>
+  <si>
+    <t>Prince George</t>
   </si>
 </sst>
 </file>
@@ -473,7 +479,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -489,14 +495,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -508,12 +511,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -811,134 +812,134 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="24" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="19" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>58</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="21" t="s">
-        <v>65</v>
+      <c r="C7" s="18" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="21" t="s">
+      <c r="A10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="19">
         <v>20171</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="21" t="s">
+      <c r="A12" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="19" t="s">
         <v>24</v>
       </c>
     </row>
@@ -957,29 +958,29 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -990,7 +991,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -1001,7 +1002,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -1012,7 +1013,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -1023,7 +1024,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -1047,29 +1048,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="11" t="s">
@@ -1080,7 +1081,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -1091,7 +1092,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -1102,7 +1103,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -1113,7 +1114,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -1124,7 +1125,7 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
@@ -1492,13 +1493,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1531,7 +1532,7 @@
       <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1539,10 +1540,10 @@
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="9" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1550,10 +1551,10 @@
       <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="9" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1573,21 +1574,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
@@ -1595,10 +1596,10 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="29" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>92</v>
       </c>
       <c r="C3">
@@ -1763,7 +1764,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="39.5703125" customWidth="1"/>
@@ -1771,101 +1772,112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="28" t="s">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C3" s="19" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="28" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="28" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C5" s="19" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="28" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C6" s="19" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="28" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C7" s="19" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="28" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C8" s="19">
         <v>20301</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="28" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C9" s="19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="28" t="s">
+    <row r="10" spans="1:3">
+      <c r="A10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C10" s="19" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1886,117 +1898,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="19" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="19" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="19" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="19" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="19" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="19">
         <v>20301</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B11" s="10" t="s">
@@ -2026,145 +2038,145 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="24" t="s">
+      <c r="A2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="19" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="19" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="19" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="18" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="21" t="s">
+      <c r="A10" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="19" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="21" t="s">
+      <c r="A12" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="19">
         <v>20171</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="21" t="s">
+      <c r="A13" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="19" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2186,108 +2198,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="21" t="s">
+      <c r="A3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="21" t="s">
+      <c r="A4" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="21" t="s">
+      <c r="A6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="19">
         <v>20301</v>
       </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="19" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="19">
         <v>1234</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2545,29 +2557,29 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="10" t="s">
@@ -2578,7 +2590,7 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
@@ -2589,7 +2601,7 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
@@ -2600,7 +2612,7 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="11" t="s">
@@ -2611,7 +2623,7 @@
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -2622,13 +2634,13 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="13" t="s">
         <v>49</v>
       </c>
     </row>

--- a/src/main/resources/UserRegistration_Field_Values.xlsx
+++ b/src/main/resources/UserRegistration_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Product\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4218C10B-D259-4A80-B736-055BF5EF2F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5119A9-01B9-47A0-98BE-973A4DAA0967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreationWithAllDetails" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="97">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -331,6 +331,12 @@
   </si>
   <si>
     <t>Prince George</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>fieldPaymentAddressCountry__c</t>
   </si>
 </sst>
 </file>
@@ -805,10 +811,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="32.42578125" customWidth="1"/>
-    <col min="3" max="3" width="51.28515625" customWidth="1"/>
+    <col min="2" max="2" width="32.453125" customWidth="1"/>
+    <col min="3" max="3" width="51.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -955,7 +961,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
@@ -1042,9 +1048,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.42578125" customWidth="1"/>
+    <col min="2" max="2" width="28.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1143,10 +1149,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1179,9 +1185,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1215,9 +1221,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1250,9 +1256,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1285,10 +1291,10 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1332,10 +1338,10 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1427,10 +1433,10 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1486,10 +1492,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1567,9 +1573,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828E63F-C4C2-4AE0-A0E9-A1CABDF6D980}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1614,10 +1620,10 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1684,10 +1690,10 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1765,9 +1771,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="39.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.54296875" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1845,7 +1851,7 @@
         <v>83</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -1890,11 +1896,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2030,11 +2036,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2190,11 +2196,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -2257,7 +2263,7 @@
         <v>74</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -2300,6 +2306,17 @@
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="16"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2310,9 +2327,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2405,11 +2422,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="43.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.26953125" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" customWidth="1"/>
+    <col min="3" max="3" width="43.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2500,7 +2517,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
@@ -2554,7 +2571,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
